--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run3/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8918,0.0362,0.0227,0.0384</t>
-  </si>
-  <si>
-    <t>0.0034,0.0016,0.0006,0.9976</t>
-  </si>
-  <si>
-    <t>0.8854,0.0005,0.0007,0.1936</t>
-  </si>
-  <si>
-    <t>0.0462,0.0027,0.0050,0.9805</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9872,0.0065,0.0016,0.0028</t>
-  </si>
-  <si>
-    <t>0.9954,0.0012,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9969,0.0006,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9860,0.0076,0.0021,0.0026</t>
-  </si>
-  <si>
-    <t>0.9905,0.0064,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9967,0.0009,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9951,0.0017,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.4702,0.0104,0.6555,0.0035</t>
-  </si>
-  <si>
-    <t>0.0493,0.0361,0.9395,0.0083</t>
-  </si>
-  <si>
-    <t>0.1716,0.0087,0.8898,0.0010</t>
-  </si>
-  <si>
-    <t>0.0040,0.0084,0.9906,0.0032</t>
-  </si>
-  <si>
-    <t>0.4737,0.0234,0.5863,0.0066</t>
-  </si>
-  <si>
-    <t>0.0156,0.9823,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.0073,0.9851,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.0299,0.9521,0.0130,0.0039</t>
-  </si>
-  <si>
-    <t>0.0118,0.9803,0.0084,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.9973,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.1491,0.0045,0.9078,0.0022</t>
-  </si>
-  <si>
-    <t>0.2800,0.0129,0.7346,0.0149</t>
-  </si>
-  <si>
-    <t>0.0033,0.0008,0.9947,0.0010</t>
-  </si>
-  <si>
-    <t>0.1423,0.0037,0.9093,0.0013</t>
-  </si>
-  <si>
-    <t>0.0087,0.0013,0.9918,0.0018</t>
-  </si>
-  <si>
-    <t>0.0090,0.0019,0.9923,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.7434,0.3391,0.0063,0.0019</t>
-  </si>
-  <si>
-    <t>0.2953,0.3037,0.5379,0.0039</t>
-  </si>
-  <si>
-    <t>0.0002,0.0081,0.9993,0.0006</t>
-  </si>
-  <si>
-    <t>0.0289,0.9127,0.0753,0.0009</t>
-  </si>
-  <si>
-    <t>0.9352,0.0329,0.0300,0.0056</t>
-  </si>
-  <si>
-    <t>0.8324,0.1545,0.0405,0.0063</t>
-  </si>
-  <si>
-    <t>0.3124,0.7780,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.0040,0.9805,0.2535,0.0036</t>
-  </si>
-  <si>
-    <t>0.0025,0.0138,0.9304,0.0622</t>
-  </si>
-  <si>
-    <t>0.0029,0.0005,0.9270,0.0585</t>
-  </si>
-  <si>
-    <t>0.0113,0.0042,0.9815,0.0046</t>
-  </si>
-  <si>
-    <t>0.0096,0.0027,0.9662,0.0304</t>
-  </si>
-  <si>
-    <t>0.0131,0.1269,0.9807,0.0013</t>
-  </si>
-  <si>
-    <t>0.0115,0.9670,0.0139,0.0033</t>
-  </si>
-  <si>
-    <t>0.0013,0.0140,0.9922,0.0044</t>
-  </si>
-  <si>
-    <t>0.0690,0.3322,0.0377,0.8603</t>
-  </si>
-  <si>
-    <t>0.0037,0.9773,0.0266,0.0749</t>
-  </si>
-  <si>
-    <t>0.0355,0.9178,0.0903,0.0027</t>
-  </si>
-  <si>
-    <t>0.0047,0.9802,0.3448,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.0090,0.9991,0.0005</t>
-  </si>
-  <si>
-    <t>0.0053,0.0425,0.9830,0.0013</t>
-  </si>
-  <si>
-    <t>0.0046,0.0018,0.9916,0.0048</t>
-  </si>
-  <si>
-    <t>0.0095,0.0003,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0023,0.9976,0.0005</t>
-  </si>
-  <si>
-    <t>0.0067,0.3226,0.8427,0.0050</t>
-  </si>
-  <si>
-    <t>0.2279,0.8289,0.0101,0.0012</t>
-  </si>
-  <si>
-    <t>0.9926,0.0011,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.9476,0.0129,0.0362,0.0054</t>
-  </si>
-  <si>
-    <t>0.0004,0.2143,0.9968,0.0070</t>
-  </si>
-  <si>
-    <t>0.9925,0.0030,0.0005,0.0019</t>
-  </si>
-  <si>
-    <t>0.9890,0.0070,0.0015,0.0020</t>
-  </si>
-  <si>
-    <t>0.9946,0.0030,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.6410,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0098,0.9940,0.0028</t>
-  </si>
-  <si>
-    <t>0.0004,0.0057,0.9986,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.8418,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9997,0.0009</t>
-  </si>
-  <si>
-    <t>0.0254,0.9645,0.0106,0.0002</t>
-  </si>
-  <si>
-    <t>0.0036,0.9944,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9724,0.0042,0.0088,0.0028</t>
-  </si>
-  <si>
-    <t>0.5204,0.1644,0.4403,0.0097</t>
-  </si>
-  <si>
-    <t>0.0021,0.0207,0.9973,0.0019</t>
-  </si>
-  <si>
-    <t>0.0014,0.9686,0.8426,0.0003</t>
-  </si>
-  <si>
-    <t>0.0030,0.2627,0.9832,0.0012</t>
-  </si>
-  <si>
-    <t>0.0019,0.9839,0.1423,0.0019</t>
-  </si>
-  <si>
-    <t>0.0003,0.9650,0.9879,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.0242,0.9966</t>
-  </si>
-  <si>
-    <t>0.0010,0.0016,0.0010,0.9988</t>
-  </si>
-  <si>
-    <t>0.0044,0.0009,0.0003,0.9978</t>
-  </si>
-  <si>
-    <t>0.0039,0.0013,0.0023,0.9960</t>
-  </si>
-  <si>
-    <t>0.0041,0.0011,0.0022,0.9962</t>
-  </si>
-  <si>
-    <t>0.0041,0.0009,0.0001,0.9980</t>
-  </si>
-  <si>
-    <t>0.0008,0.9260,0.9790,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.8965,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0255,0.0983,0.8593,0.0060</t>
-  </si>
-  <si>
-    <t>0.0018,0.5732,0.9886,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.8589,0.9825,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9620,0.9444,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0014,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9634,0.0588,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9767,0.0255,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.9828,0.0142,0.0028,0.0021</t>
-  </si>
-  <si>
-    <t>0.9843,0.0094,0.0030,0.0026</t>
-  </si>
-  <si>
-    <t>0.9921,0.0029,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9895,0.0034,0.0011,0.0040</t>
-  </si>
-  <si>
-    <t>0.9902,0.0071,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9909,0.0030,0.0021,0.0026</t>
-  </si>
-  <si>
-    <t>0.9929,0.0022,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9956,0.0006,0.0001,0.0019</t>
-  </si>
-  <si>
-    <t>0.9942,0.0016,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9966,0.0006,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9920,0.0053,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9947,0.0013,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9969,0.0212</t>
-  </si>
-  <si>
-    <t>0.0050,0.0019,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.8458,0.0067,0.0156,0.1053</t>
-  </si>
-  <si>
-    <t>0.0033,0.0021,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.0120,0.9804,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.0040,0.9895,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.0065,0.9837,0.0129,0.0014</t>
-  </si>
-  <si>
-    <t>0.0098,0.9803,0.0288,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9941,0.0087,0.0021</t>
-  </si>
-  <si>
-    <t>0.0020,0.9940,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.1978,0.8446,0.0046,0.0005</t>
-  </si>
-  <si>
-    <t>0.6876,0.1210,0.2572,0.0269</t>
-  </si>
-  <si>
-    <t>0.2709,0.0042,0.8325,0.0019</t>
-  </si>
-  <si>
-    <t>0.5212,0.0937,0.3605,0.0446</t>
-  </si>
-  <si>
-    <t>0.5338,0.0912,0.4212,0.0169</t>
-  </si>
-  <si>
-    <t>0.0072,0.0395,0.0099,0.9854</t>
-  </si>
-  <si>
-    <t>0.0075,0.9864,0.0283,0.0003</t>
-  </si>
-  <si>
-    <t>0.0081,0.9804,0.0210,0.0021</t>
-  </si>
-  <si>
-    <t>0.0067,0.9788,0.0932,0.0045</t>
-  </si>
-  <si>
-    <t>0.0031,0.9624,0.8164,0.0017</t>
-  </si>
-  <si>
-    <t>0.0081,0.9899,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0565,0.9349,0.0245,0.0025</t>
-  </si>
-  <si>
-    <t>0.8213,0.2362,0.0072,0.0008</t>
-  </si>
-  <si>
-    <t>0.9889,0.0012,0.0043,0.0011</t>
-  </si>
-  <si>
-    <t>0.9946,0.0003,0.0002,0.0030</t>
-  </si>
-  <si>
-    <t>0.9913,0.0020,0.0006,0.0034</t>
-  </si>
-  <si>
-    <t>0.9948,0.0006,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9962,0.0007,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9943,0.0010,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.9907,0.0061,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9939,0.0010,0.0003,0.0027</t>
-  </si>
-  <si>
-    <t>0.0009,0.3919,0.9955,0.0007</t>
-  </si>
-  <si>
-    <t>0.0042,0.2675,0.9734,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0083,0.9962,0.0008</t>
-  </si>
-  <si>
-    <t>0.0020,0.0252,0.9939,0.0010</t>
-  </si>
-  <si>
-    <t>0.7145,0.0101,0.1146,0.0898</t>
-  </si>
-  <si>
-    <t>0.8451,0.0111,0.0782,0.0275</t>
-  </si>
-  <si>
-    <t>0.3326,0.0001,0.8630,0.0003</t>
-  </si>
-  <si>
-    <t>0.6768,0.1357,0.2152,0.0387</t>
-  </si>
-  <si>
-    <t>0.0545,0.0013,0.0032,0.9785</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0004,0.9998</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.0129,0.9973</t>
-  </si>
-  <si>
-    <t>0.0047,0.0003,0.0004,0.9980</t>
-  </si>
-  <si>
-    <t>0.0022,0.8010,0.9350,0.0015</t>
-  </si>
-  <si>
-    <t>0.9909,0.0012,0.0006,0.0039</t>
-  </si>
-  <si>
-    <t>0.0650,0.9158,0.0047,0.0104</t>
-  </si>
-  <si>
-    <t>0.9904,0.0021,0.0013,0.0024</t>
-  </si>
-  <si>
-    <t>0.7744,0.2069,0.0341,0.0064</t>
-  </si>
-  <si>
-    <t>0.9825,0.0009,0.0008,0.0097</t>
-  </si>
-  <si>
-    <t>0.5453,0.0387,0.0396,0.5392</t>
-  </si>
-  <si>
-    <t>0.9921,0.0021,0.0009,0.0017</t>
-  </si>
-  <si>
-    <t>0.0018,0.3992,0.9513,0.0243</t>
-  </si>
-  <si>
-    <t>0.9306,0.0007,0.0056,0.0577</t>
-  </si>
-  <si>
-    <t>0.8783,0.0039,0.0249,0.0799</t>
-  </si>
-  <si>
-    <t>0.6382,0.3720,0.0253,0.0043</t>
-  </si>
-  <si>
-    <t>0.9895,0.0026,0.0023,0.0007</t>
-  </si>
-  <si>
-    <t>0.9746,0.0039,0.0140,0.0005</t>
-  </si>
-  <si>
-    <t>0.0771,0.6715,0.2051,0.0571</t>
-  </si>
-  <si>
-    <t>0.3549,0.5837,0.1348,0.0363</t>
-  </si>
-  <si>
-    <t>0.9203,0.0515,0.0291,0.0055</t>
-  </si>
-  <si>
-    <t>0.9869,0.0047,0.0019,0.0029</t>
-  </si>
-  <si>
-    <t>0.9954,0.0009,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9975,0.0002,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9899,0.0023,0.0019,0.0030</t>
-  </si>
-  <si>
-    <t>0.9947,0.0016,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9933,0.0036,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9956,0.0007,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9729,0.0072,0.0011,0.0096</t>
-  </si>
-  <si>
-    <t>0.5652,0.6189,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.1761,0.8219,0.0289,0.0026</t>
-  </si>
-  <si>
-    <t>0.6643,0.4303,0.0144,0.0021</t>
-  </si>
-  <si>
-    <t>0.9288,0.0494,0.0225,0.0099</t>
-  </si>
-  <si>
-    <t>0.9789,0.0205,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9892,0.0064,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9730,0.0173,0.0052,0.0021</t>
-  </si>
-  <si>
-    <t>0.9472,0.0612,0.0054,0.0023</t>
-  </si>
-  <si>
-    <t>0.0005,0.0220,0.9988,0.0007</t>
-  </si>
-  <si>
-    <t>0.8945,0.0872,0.0219,0.0075</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9985,0.0015</t>
-  </si>
-  <si>
-    <t>0.0018,0.0091,0.9956,0.0008</t>
-  </si>
-  <si>
-    <t>0.0516,0.0032,0.9552,0.0077</t>
-  </si>
-  <si>
-    <t>0.0028,0.0050,0.9959,0.0006</t>
-  </si>
-  <si>
-    <t>0.0024,0.0062,0.9920,0.0070</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.0125,0.9912,0.0034</t>
-  </si>
-  <si>
-    <t>0.0403,0.0031,0.9734,0.0010</t>
-  </si>
-  <si>
-    <t>0.1062,0.0021,0.9247,0.0024</t>
-  </si>
-  <si>
-    <t>0.0883,0.0134,0.8892,0.0469</t>
-  </si>
-  <si>
-    <t>0.0199,0.0367,0.9587,0.0017</t>
-  </si>
-  <si>
-    <t>0.0894,0.5187,0.4626,0.0039</t>
-  </si>
-  <si>
-    <t>0.7951,0.0021,0.3092,0.0003</t>
-  </si>
-  <si>
-    <t>0.5723,0.0443,0.4494,0.0371</t>
-  </si>
-  <si>
-    <t>0.5004,0.0630,0.4866,0.0933</t>
-  </si>
-  <si>
-    <t>0.2224,0.8175,0.0030,0.0023</t>
-  </si>
-  <si>
-    <t>0.3050,0.7681,0.0020,0.0020</t>
-  </si>
-  <si>
-    <t>0.9279,0.1300,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.1759,0.8808,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.1677,0.8982,0.0022,0.0005</t>
-  </si>
-  <si>
-    <t>0.9591,0.0071,0.0230,0.0004</t>
-  </si>
-  <si>
-    <t>0.9738,0.0009,0.0192,0.0005</t>
-  </si>
-  <si>
-    <t>0.9387,0.0016,0.0151,0.0149</t>
-  </si>
-  <si>
-    <t>0.5532,0.0035,0.6386,0.0014</t>
-  </si>
-  <si>
-    <t>0.8678,0.0011,0.1710,0.0015</t>
-  </si>
-  <si>
-    <t>0.0359,0.0015,0.9667,0.0074</t>
-  </si>
-  <si>
-    <t>0.0170,0.0715,0.8402,0.0637</t>
-  </si>
-  <si>
-    <t>0.0188,0.0259,0.9687,0.0028</t>
-  </si>
-  <si>
-    <t>0.0432,0.0052,0.9684,0.0009</t>
-  </si>
-  <si>
-    <t>0.0067,0.0197,0.9867,0.0023</t>
-  </si>
-  <si>
-    <t>0.9865,0.0056,0.0018,0.0039</t>
-  </si>
-  <si>
-    <t>0.9954,0.0006,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9819,0.0132,0.0022,0.0054</t>
-  </si>
-  <si>
-    <t>0.9744,0.0319,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.9167,0.0745,0.0232,0.0094</t>
-  </si>
-  <si>
-    <t>0.9899,0.0057,0.0011,0.0021</t>
-  </si>
-  <si>
-    <t>0.9963,0.0005,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9875,0.0057,0.0017,0.0031</t>
-  </si>
-  <si>
-    <t>0.0033,0.0109,0.9961,0.0011</t>
-  </si>
-  <si>
-    <t>0.6964,0.1029,0.2803,0.0153</t>
-  </si>
-  <si>
-    <t>0.2142,0.2881,0.3107,0.2690</t>
-  </si>
-  <si>
-    <t>0.0007,0.0008,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9975,0.0104</t>
-  </si>
-  <si>
-    <t>0.0114,0.1293,0.9531,0.0052</t>
-  </si>
-  <si>
-    <t>0.0006,0.0013,0.9985,0.0012</t>
-  </si>
-  <si>
-    <t>0.0018,0.0100,0.9938,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0018,0.9936,0.0014</t>
-  </si>
-  <si>
-    <t>0.0113,0.0211,0.9821,0.0033</t>
-  </si>
-  <si>
-    <t>0.8452,0.0027,0.1571,0.0055</t>
-  </si>
-  <si>
-    <t>0.3112,0.0004,0.7165,0.0035</t>
-  </si>
-  <si>
-    <t>0.9787,0.0007,0.0114,0.0011</t>
-  </si>
-  <si>
-    <t>0.9903,0.0036,0.0006,0.0042</t>
-  </si>
-  <si>
-    <t>0.9850,0.0075,0.0017,0.0027</t>
-  </si>
-  <si>
-    <t>0.9910,0.0030,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.9767,0.0220,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.9928,0.0030,0.0008,0.0023</t>
-  </si>
-  <si>
-    <t>0.9930,0.0021,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9944,0.0032,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9946,0.0018,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.0135,0.0696,0.9402,0.0045</t>
-  </si>
-  <si>
-    <t>0.0073,0.0354,0.9909,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0055,0.9935,0.0020</t>
-  </si>
-  <si>
-    <t>0.0365,0.0273,0.9235,0.0020</t>
-  </si>
-  <si>
-    <t>0.0033,0.0001,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0429,0.0042,0.9021,0.0613</t>
-  </si>
-  <si>
-    <t>0.0989,0.0286,0.9081,0.0030</t>
-  </si>
-  <si>
-    <t>0.5457,0.0467,0.3239,0.1326</t>
-  </si>
-  <si>
-    <t>0.9158,0.0009,0.0080,0.0628</t>
-  </si>
-  <si>
-    <t>0.0103,0.0089,0.0029,0.9917</t>
-  </si>
-  <si>
-    <t>0.0447,0.0026,0.0006,0.9815</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0003,0.9994</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.0013,0.9989</t>
-  </si>
-  <si>
-    <t>0.8276,0.0036,0.0018,0.2956</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9483,0.0155,0.0181,0.0081</t>
+  </si>
+  <si>
+    <t>0.0171,0.0010,0.0007,0.9931</t>
+  </si>
+  <si>
+    <t>0.9782,0.0008,0.0002,0.0182</t>
+  </si>
+  <si>
+    <t>0.1074,0.0031,0.0026,0.9628</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0023,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9919,0.0041,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9944,0.0027,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9892,0.0072,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.9900,0.0060,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.8798,0.0089,0.1443,0.0021</t>
+  </si>
+  <si>
+    <t>0.0497,0.0022,0.9737,0.0007</t>
+  </si>
+  <si>
+    <t>0.0332,0.0024,0.9791,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.0069,0.9917,0.0048</t>
+  </si>
+  <si>
+    <t>0.9136,0.0044,0.0763,0.0035</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0089,0.9788,0.0113,0.0024</t>
+  </si>
+  <si>
+    <t>0.0222,0.9628,0.0262,0.0040</t>
+  </si>
+  <si>
+    <t>0.0157,0.9778,0.0082,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.9975,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.5682,0.0018,0.4463,0.0072</t>
+  </si>
+  <si>
+    <t>0.3420,0.0039,0.7834,0.0027</t>
+  </si>
+  <si>
+    <t>0.0023,0.0005,0.9964,0.0005</t>
+  </si>
+  <si>
+    <t>0.0300,0.0031,0.9783,0.0006</t>
+  </si>
+  <si>
+    <t>0.0374,0.0065,0.9735,0.0014</t>
+  </si>
+  <si>
+    <t>0.0041,0.0007,0.9942,0.0028</t>
+  </si>
+  <si>
+    <t>0.0064,0.0011,0.9952,0.0007</t>
+  </si>
+  <si>
+    <t>0.7129,0.4069,0.0051,0.0012</t>
+  </si>
+  <si>
+    <t>0.4736,0.3335,0.2626,0.0076</t>
+  </si>
+  <si>
+    <t>0.0010,0.0151,0.9982,0.0013</t>
+  </si>
+  <si>
+    <t>0.0085,0.9459,0.0974,0.0001</t>
+  </si>
+  <si>
+    <t>0.7203,0.1715,0.1621,0.0169</t>
+  </si>
+  <si>
+    <t>0.7686,0.1491,0.0584,0.0064</t>
+  </si>
+  <si>
+    <t>0.7585,0.3350,0.0092,0.0011</t>
+  </si>
+  <si>
+    <t>0.0368,0.8377,0.7029,0.0064</t>
+  </si>
+  <si>
+    <t>0.0042,0.1530,0.9423,0.0043</t>
+  </si>
+  <si>
+    <t>0.0048,0.0004,0.8882,0.0520</t>
+  </si>
+  <si>
+    <t>0.0430,0.0041,0.9766,0.0006</t>
+  </si>
+  <si>
+    <t>0.0677,0.0015,0.8789,0.0205</t>
+  </si>
+  <si>
+    <t>0.0142,0.0557,0.9872,0.0004</t>
+  </si>
+  <si>
+    <t>0.0280,0.9174,0.0273,0.0033</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9976,0.0043</t>
+  </si>
+  <si>
+    <t>0.1074,0.0978,0.0012,0.7568</t>
+  </si>
+  <si>
+    <t>0.0041,0.9809,0.0092,0.0357</t>
+  </si>
+  <si>
+    <t>0.0147,0.9734,0.0090,0.0007</t>
+  </si>
+  <si>
+    <t>0.0056,0.9849,0.0291,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0030,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.1551,0.9948,0.0008</t>
+  </si>
+  <si>
+    <t>0.0674,0.0018,0.9404,0.0055</t>
+  </si>
+  <si>
+    <t>0.0114,0.0004,0.9938,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.0080,0.9934,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.0255,0.9927,0.0004</t>
+  </si>
+  <si>
+    <t>0.9345,0.0727,0.0067,0.0041</t>
+  </si>
+  <si>
+    <t>0.9815,0.0040,0.0070,0.0022</t>
+  </si>
+  <si>
+    <t>0.9726,0.0091,0.0088,0.0060</t>
+  </si>
+  <si>
+    <t>0.0006,0.1068,0.9972,0.0099</t>
+  </si>
+  <si>
+    <t>0.9653,0.0154,0.0149,0.0032</t>
+  </si>
+  <si>
+    <t>0.9890,0.0055,0.0015,0.0025</t>
+  </si>
+  <si>
+    <t>0.9833,0.0175,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.5105,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0658,0.9936,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0023,0.9995,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.5280,0.9936,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0160,0.9732,0.0132,0.0003</t>
+  </si>
+  <si>
+    <t>0.0102,0.9887,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9012,0.0059,0.1402,0.0010</t>
+  </si>
+  <si>
+    <t>0.7427,0.2713,0.0374,0.0038</t>
+  </si>
+  <si>
+    <t>0.0010,0.0634,0.9970,0.0022</t>
+  </si>
+  <si>
+    <t>0.0014,0.9434,0.9229,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.7920,0.9885,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9662,0.0612,0.0167</t>
+  </si>
+  <si>
+    <t>0.0002,0.9855,0.9825,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0100,0.9975</t>
+  </si>
+  <si>
+    <t>0.0003,0.0042,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0030,0.0003,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0026,0.0006,0.0091,0.9947</t>
+  </si>
+  <si>
+    <t>0.0045,0.0011,0.0054,0.9940</t>
+  </si>
+  <si>
+    <t>0.0040,0.0007,0.0133,0.9910</t>
+  </si>
+  <si>
+    <t>0.0005,0.9819,0.8698,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.4925,0.9856,0.0013</t>
+  </si>
+  <si>
+    <t>0.0029,0.0589,0.9484,0.0130</t>
+  </si>
+  <si>
+    <t>0.0055,0.2682,0.9602,0.0036</t>
+  </si>
+  <si>
+    <t>0.0015,0.6857,0.9857,0.0004</t>
+  </si>
+  <si>
+    <t>0.0055,0.7133,0.8587,0.0019</t>
+  </si>
+  <si>
+    <t>0.9945,0.0017,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9905,0.0090,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9847,0.0115,0.0022,0.0020</t>
+  </si>
+  <si>
+    <t>0.9869,0.0085,0.0013,0.0029</t>
+  </si>
+  <si>
+    <t>0.9782,0.0131,0.0050,0.0029</t>
+  </si>
+  <si>
+    <t>0.9858,0.0115,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9770,0.0123,0.0037,0.0083</t>
+  </si>
+  <si>
+    <t>0.9886,0.0036,0.0041,0.0011</t>
+  </si>
+  <si>
+    <t>0.9973,0.0003,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9956,0.0008,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9977,0.0002,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0018,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9945,0.0013,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9892,0.0026,0.0016,0.0037</t>
+  </si>
+  <si>
+    <t>0.9942,0.0020,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9992,0.0019</t>
+  </si>
+  <si>
+    <t>0.1494,0.0174,0.8986,0.0018</t>
+  </si>
+  <si>
+    <t>0.9203,0.0008,0.0053,0.0404</t>
+  </si>
+  <si>
+    <t>0.0019,0.0025,0.9965,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.9898,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.0041,0.9912,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.9921,0.0087,0.0017</t>
+  </si>
+  <si>
+    <t>0.1664,0.8568,0.0148,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.9959,0.0098,0.0006</t>
+  </si>
+  <si>
+    <t>0.0057,0.9886,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.1458,0.8932,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.8395,0.0153,0.1423,0.0100</t>
+  </si>
+  <si>
+    <t>0.2413,0.0025,0.7439,0.0179</t>
+  </si>
+  <si>
+    <t>0.3996,0.0868,0.5311,0.0800</t>
+  </si>
+  <si>
+    <t>0.0569,0.0110,0.9552,0.0014</t>
+  </si>
+  <si>
+    <t>0.0122,0.0155,0.0340,0.9810</t>
+  </si>
+  <si>
+    <t>0.0053,0.9852,0.0315,0.0015</t>
+  </si>
+  <si>
+    <t>0.0057,0.9784,0.0277,0.0084</t>
+  </si>
+  <si>
+    <t>0.0022,0.9901,0.0021,0.0096</t>
+  </si>
+  <si>
+    <t>0.0059,0.9789,0.1498,0.0036</t>
+  </si>
+  <si>
+    <t>0.0333,0.9652,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.1993,0.8185,0.0240,0.0037</t>
+  </si>
+  <si>
+    <t>0.3459,0.6764,0.0099,0.0038</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9932,0.0019,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9951,0.0013,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9807,0.0095,0.0043,0.0037</t>
+  </si>
+  <si>
+    <t>0.9955,0.0006,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9911,0.0019,0.0039,0.0006</t>
+  </si>
+  <si>
+    <t>0.9767,0.0079,0.0031,0.0092</t>
+  </si>
+  <si>
+    <t>0.9953,0.0029,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.2117,0.9947,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.1784,0.9836,0.0002</t>
+  </si>
+  <si>
+    <t>0.0094,0.0163,0.9824,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.0387,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.9697,0.0024,0.0148,0.0014</t>
+  </si>
+  <si>
+    <t>0.8608,0.0036,0.1717,0.0020</t>
+  </si>
+  <si>
+    <t>0.1134,0.0006,0.9641,0.0003</t>
+  </si>
+  <si>
+    <t>0.2715,0.0250,0.7964,0.0045</t>
+  </si>
+  <si>
+    <t>0.0102,0.0009,0.0010,0.9952</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0007,0.9998</t>
+  </si>
+  <si>
+    <t>0.0015,0.0018,0.0043,0.9976</t>
+  </si>
+  <si>
+    <t>0.0035,0.0002,0.0002,0.9989</t>
+  </si>
+  <si>
+    <t>0.0012,0.9375,0.7886,0.0015</t>
+  </si>
+  <si>
+    <t>0.9947,0.0009,0.0003,0.0028</t>
+  </si>
+  <si>
+    <t>0.3249,0.5796,0.0588,0.0087</t>
+  </si>
+  <si>
+    <t>0.9869,0.0019,0.0014,0.0078</t>
+  </si>
+  <si>
+    <t>0.0737,0.9097,0.0270,0.0016</t>
+  </si>
+  <si>
+    <t>0.9895,0.0007,0.0017,0.0036</t>
+  </si>
+  <si>
+    <t>0.7152,0.0595,0.0427,0.2740</t>
+  </si>
+  <si>
+    <t>0.9950,0.0010,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.0045,0.3371,0.9656,0.0138</t>
+  </si>
+  <si>
+    <t>0.9627,0.0008,0.0020,0.0407</t>
+  </si>
+  <si>
+    <t>0.9773,0.0018,0.0078,0.0047</t>
+  </si>
+  <si>
+    <t>0.2337,0.7318,0.0492,0.0106</t>
+  </si>
+  <si>
+    <t>0.9751,0.0043,0.0093,0.0018</t>
+  </si>
+  <si>
+    <t>0.9493,0.0236,0.0157,0.0063</t>
+  </si>
+  <si>
+    <t>0.4730,0.5910,0.0138,0.0042</t>
+  </si>
+  <si>
+    <t>0.8446,0.0614,0.1058,0.0050</t>
+  </si>
+  <si>
+    <t>0.9715,0.0264,0.0041,0.0009</t>
+  </si>
+  <si>
+    <t>0.9810,0.0093,0.0047,0.0027</t>
+  </si>
+  <si>
+    <t>0.9793,0.0064,0.0009,0.0113</t>
+  </si>
+  <si>
+    <t>0.9938,0.0013,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9900,0.0015,0.0021,0.0031</t>
+  </si>
+  <si>
+    <t>0.9936,0.0013,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9808,0.0167,0.0030,0.0017</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9925,0.0026,0.0012,0.0015</t>
+  </si>
+  <si>
+    <t>0.7387,0.3505,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.4658,0.5889,0.0277,0.0020</t>
+  </si>
+  <si>
+    <t>0.5233,0.4657,0.0473,0.0021</t>
+  </si>
+  <si>
+    <t>0.0209,0.4343,0.9477,0.0029</t>
+  </si>
+  <si>
+    <t>0.9788,0.0221,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9853,0.0042,0.0013,0.0041</t>
+  </si>
+  <si>
+    <t>0.9581,0.0479,0.0039,0.0019</t>
+  </si>
+  <si>
+    <t>0.9777,0.0122,0.0024,0.0036</t>
+  </si>
+  <si>
+    <t>0.0007,0.0128,0.9991,0.0008</t>
+  </si>
+  <si>
+    <t>0.9338,0.0946,0.0025,0.0012</t>
+  </si>
+  <si>
+    <t>0.0025,0.0003,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.0074,0.9878,0.0020</t>
+  </si>
+  <si>
+    <t>0.0059,0.0025,0.9934,0.0009</t>
+  </si>
+  <si>
+    <t>0.0065,0.0869,0.9758,0.0017</t>
+  </si>
+  <si>
+    <t>0.0033,0.0035,0.9955,0.0014</t>
+  </si>
+  <si>
+    <t>0.0018,0.0005,0.9980,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.0017,0.9963,0.0005</t>
+  </si>
+  <si>
+    <t>0.0702,0.0072,0.9451,0.0090</t>
+  </si>
+  <si>
+    <t>0.0555,0.0091,0.9550,0.0021</t>
+  </si>
+  <si>
+    <t>0.2843,0.0057,0.8347,0.0010</t>
+  </si>
+  <si>
+    <t>0.0981,0.0203,0.9029,0.0012</t>
+  </si>
+  <si>
+    <t>0.0380,0.1048,0.8772,0.0029</t>
+  </si>
+  <si>
+    <t>0.5521,0.0127,0.5171,0.0006</t>
+  </si>
+  <si>
+    <t>0.7816,0.0176,0.1809,0.0191</t>
+  </si>
+  <si>
+    <t>0.0239,0.0096,0.9805,0.0009</t>
+  </si>
+  <si>
+    <t>0.2551,0.8321,0.0042,0.0006</t>
+  </si>
+  <si>
+    <t>0.0340,0.9629,0.0074,0.0006</t>
+  </si>
+  <si>
+    <t>0.8619,0.1751,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.5793,0.4859,0.0027,0.0033</t>
+  </si>
+  <si>
+    <t>0.1540,0.8850,0.0045,0.0010</t>
+  </si>
+  <si>
+    <t>0.6470,0.0235,0.4609,0.0028</t>
+  </si>
+  <si>
+    <t>0.8368,0.0097,0.1405,0.0112</t>
+  </si>
+  <si>
+    <t>0.9820,0.0007,0.0059,0.0012</t>
+  </si>
+  <si>
+    <t>0.8800,0.0031,0.1981,0.0013</t>
+  </si>
+  <si>
+    <t>0.6286,0.0140,0.4297,0.0115</t>
+  </si>
+  <si>
+    <t>0.0108,0.0061,0.9772,0.0390</t>
+  </si>
+  <si>
+    <t>0.0033,0.0237,0.9872,0.0058</t>
+  </si>
+  <si>
+    <t>0.0017,0.0021,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.1830,0.0023,0.9027,0.0005</t>
+  </si>
+  <si>
+    <t>0.0052,0.0845,0.9820,0.0016</t>
+  </si>
+  <si>
+    <t>0.9769,0.0044,0.0052,0.0102</t>
+  </si>
+  <si>
+    <t>0.9943,0.0023,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9869,0.0116,0.0011,0.0019</t>
+  </si>
+  <si>
+    <t>0.9833,0.0104,0.0007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9892,0.0057,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.9916,0.0043,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9873,0.0018,0.0016,0.0072</t>
+  </si>
+  <si>
+    <t>0.9937,0.0012,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.0578,0.9945,0.0023</t>
+  </si>
+  <si>
+    <t>0.0210,0.2476,0.8989,0.0042</t>
+  </si>
+  <si>
+    <t>0.9649,0.0020,0.0137,0.0076</t>
+  </si>
+  <si>
+    <t>0.0015,0.0026,0.9971,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9970,0.0186</t>
+  </si>
+  <si>
+    <t>0.0201,0.0478,0.9574,0.0054</t>
+  </si>
+  <si>
+    <t>0.0007,0.0025,0.9991,0.0006</t>
+  </si>
+  <si>
+    <t>0.0645,0.0042,0.9467,0.0036</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.0061,0.9921,0.0019</t>
+  </si>
+  <si>
+    <t>0.0317,0.0250,0.9564,0.0057</t>
+  </si>
+  <si>
+    <t>0.4992,0.0003,0.5022,0.0057</t>
+  </si>
+  <si>
+    <t>0.9078,0.0004,0.1364,0.0007</t>
+  </si>
+  <si>
+    <t>0.9896,0.0003,0.0048,0.0003</t>
+  </si>
+  <si>
+    <t>0.9929,0.0019,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9869,0.0083,0.0018,0.0013</t>
+  </si>
+  <si>
+    <t>0.9882,0.0029,0.0030,0.0018</t>
+  </si>
+  <si>
+    <t>0.9819,0.0117,0.0039,0.0024</t>
+  </si>
+  <si>
+    <t>0.9886,0.0006,0.0003,0.0135</t>
+  </si>
+  <si>
+    <t>0.9917,0.0048,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9739,0.0337,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9667,0.0279,0.0027,0.0041</t>
+  </si>
+  <si>
+    <t>0.0058,0.0107,0.9849,0.0040</t>
+  </si>
+  <si>
+    <t>0.0010,0.0036,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0043,0.0045,0.9935,0.0015</t>
+  </si>
+  <si>
+    <t>0.0265,0.0128,0.9765,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0857,0.0154,0.8227,0.0852</t>
+  </si>
+  <si>
+    <t>0.0406,0.0087,0.9507,0.0102</t>
+  </si>
+  <si>
+    <t>0.3859,0.0124,0.5670,0.0266</t>
+  </si>
+  <si>
+    <t>0.9449,0.0003,0.0079,0.0151</t>
+  </si>
+  <si>
+    <t>0.0278,0.0078,0.0009,0.9878</t>
+  </si>
+  <si>
+    <t>0.0136,0.0014,0.0009,0.9932</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0013,0.0002,0.0003,0.9992</t>
+  </si>
+  <si>
+    <t>0.8242,0.0047,0.0024,0.2448</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2463,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,10 +2715,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2967,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3107,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3667,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4745,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
